--- a/data/busan-energy-teacher-data.xlsx
+++ b/data/busan-energy-teacher-data.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="648">
   <si>
     <r>
       <rPr>
@@ -2323,6 +2323,9 @@
     <t xml:space="preserve">수소연료전지 보급</t>
   </si>
   <si>
+    <t xml:space="preserve">수소연료전지 설치</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2421,16 +2424,16 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">설비 용량</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(MW), </t>
+      <t xml:space="preserve">설치 용량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(kW), </t>
     </r>
     <r>
       <rPr>
@@ -2447,7 +2450,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(MWh)</t>
+      <t xml:space="preserve">(kWh), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필요한 연료 에너지</t>
     </r>
   </si>
   <si>
@@ -4327,6 +4338,9 @@
     <t xml:space="preserve">시민참여형 발전사업 활성화</t>
   </si>
   <si>
+    <t xml:space="preserve">시민참여 미니태양광 지원</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -4448,6 +4462,23 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">참여 의향이 있다는 응답은 실제 참여나 투자와 다릅니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차시에서 참여율을 바꿔 실행하면 예산이 남는 경우를 확인할 수 있습니다</t>
     </r>
     <r>
       <rPr>
@@ -15541,6 +15572,85 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">• 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차시 시뮬레이터에서 미니태양광 참여율을 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">81%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">와 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 바꿔 실행해 보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과가 어떻게 달라지는지 설명해 보자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
   </si>
   <si>
@@ -19281,11 +19391,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="52363966"/>
-        <c:axId val="26640965"/>
+        <c:axId val="39251896"/>
+        <c:axId val="29905600"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="52363966"/>
+        <c:axId val="39251896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19317,7 +19427,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26640965"/>
+        <c:crossAx val="29905600"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -19325,7 +19435,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="26640965"/>
+        <c:axId val="29905600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19401,7 +19511,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52363966"/>
+        <c:crossAx val="39251896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19638,11 +19748,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="58003032"/>
-        <c:axId val="76836799"/>
+        <c:axId val="92791558"/>
+        <c:axId val="80891113"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="58003032"/>
+        <c:axId val="92791558"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19674,7 +19784,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76836799"/>
+        <c:crossAx val="80891113"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -19682,7 +19792,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76836799"/>
+        <c:axId val="80891113"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19758,7 +19868,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58003032"/>
+        <c:crossAx val="92791558"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19935,11 +20045,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="95491096"/>
-        <c:axId val="56310653"/>
+        <c:axId val="65943338"/>
+        <c:axId val="3436774"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="95491096"/>
+        <c:axId val="65943338"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19971,7 +20081,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56310653"/>
+        <c:crossAx val="3436774"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -19979,7 +20089,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56310653"/>
+        <c:axId val="3436774"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20055,7 +20165,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95491096"/>
+        <c:crossAx val="65943338"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20406,11 +20516,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="21982478"/>
-        <c:axId val="47850040"/>
+        <c:axId val="27319620"/>
+        <c:axId val="30894230"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="21982478"/>
+        <c:axId val="27319620"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20442,7 +20552,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47850040"/>
+        <c:crossAx val="30894230"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -20450,7 +20560,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="47850040"/>
+        <c:axId val="30894230"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20526,7 +20636,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21982478"/>
+        <c:crossAx val="27319620"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20709,11 +20819,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="46052109"/>
-        <c:axId val="41217533"/>
+        <c:axId val="1691639"/>
+        <c:axId val="90164455"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="46052109"/>
+        <c:axId val="1691639"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20745,7 +20855,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41217533"/>
+        <c:crossAx val="90164455"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -20753,7 +20863,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41217533"/>
+        <c:axId val="90164455"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20829,7 +20939,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46052109"/>
+        <c:crossAx val="1691639"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -21365,11 +21475,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="31022502"/>
-        <c:axId val="44116729"/>
+        <c:axId val="41254945"/>
+        <c:axId val="76221491"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="31022502"/>
+        <c:axId val="41254945"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -21401,7 +21511,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44116729"/>
+        <c:crossAx val="76221491"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -21409,7 +21519,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44116729"/>
+        <c:axId val="76221491"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -21485,7 +21595,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31022502"/>
+        <c:crossAx val="41254945"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -22021,11 +22131,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="50995122"/>
-        <c:axId val="162175"/>
+        <c:axId val="48627952"/>
+        <c:axId val="68870586"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="50995122"/>
+        <c:axId val="48627952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22057,7 +22167,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="162175"/>
+        <c:crossAx val="68870586"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -22065,7 +22175,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="162175"/>
+        <c:axId val="68870586"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22141,7 +22251,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50995122"/>
+        <c:crossAx val="48627952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -22516,11 +22626,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="91712505"/>
-        <c:axId val="48989783"/>
+        <c:axId val="11537016"/>
+        <c:axId val="74691838"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="91712505"/>
+        <c:axId val="11537016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22552,7 +22662,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48989783"/>
+        <c:crossAx val="74691838"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -22560,7 +22670,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48989783"/>
+        <c:axId val="74691838"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22636,7 +22746,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91712505"/>
+        <c:crossAx val="11537016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -22873,11 +22983,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="55724807"/>
-        <c:axId val="5344591"/>
+        <c:axId val="5091141"/>
+        <c:axId val="37562803"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="55724807"/>
+        <c:axId val="5091141"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22909,7 +23019,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5344591"/>
+        <c:crossAx val="37562803"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -22917,7 +23027,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="5344591"/>
+        <c:axId val="37562803"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22993,7 +23103,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55724807"/>
+        <c:crossAx val="5091141"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -23230,11 +23340,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="60431234"/>
-        <c:axId val="57400850"/>
+        <c:axId val="6919180"/>
+        <c:axId val="11152629"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="60431234"/>
+        <c:axId val="6919180"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -23266,7 +23376,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57400850"/>
+        <c:crossAx val="11152629"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -23274,7 +23384,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="57400850"/>
+        <c:axId val="11152629"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -23350,7 +23460,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60431234"/>
+        <c:crossAx val="6919180"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -23533,11 +23643,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="80396765"/>
-        <c:axId val="43584939"/>
+        <c:axId val="64184646"/>
+        <c:axId val="89479679"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="80396765"/>
+        <c:axId val="64184646"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -23569,7 +23679,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43584939"/>
+        <c:crossAx val="89479679"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -23577,7 +23687,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43584939"/>
+        <c:axId val="89479679"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -23653,7 +23763,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80396765"/>
+        <c:crossAx val="64184646"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -23836,11 +23946,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="69530444"/>
-        <c:axId val="37512359"/>
+        <c:axId val="12928499"/>
+        <c:axId val="83618270"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="69530444"/>
+        <c:axId val="12928499"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -23872,7 +23982,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37512359"/>
+        <c:crossAx val="83618270"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -23880,7 +23990,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37512359"/>
+        <c:axId val="83618270"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -23956,7 +24066,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69530444"/>
+        <c:crossAx val="12928499"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -24864,15 +24974,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -24883,10 +24993,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -24897,10 +25007,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -24914,7 +25024,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -24928,7 +25038,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -24942,7 +25052,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
@@ -24956,7 +25066,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -24967,68 +25077,68 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -25040,7 +25150,7 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -25052,12 +25162,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
@@ -25069,7 +25179,7 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -25081,12 +25191,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -25098,7 +25208,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -25157,15 +25267,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -25176,10 +25286,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -25190,10 +25300,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -25207,7 +25317,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -25221,7 +25331,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -25232,15 +25342,15 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>50</v>
@@ -25248,7 +25358,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>130</v>
@@ -25256,7 +25366,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>300</v>
@@ -25267,68 +25377,68 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
@@ -25340,7 +25450,7 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -25352,12 +25462,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -25369,7 +25479,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -25381,12 +25491,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -25398,7 +25508,7 @@
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -25454,15 +25564,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -25473,10 +25583,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -25487,10 +25597,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -25504,7 +25614,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -25518,7 +25628,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -25529,7 +25639,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -25541,7 +25651,7 @@
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -25553,7 +25663,7 @@
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -25565,12 +25675,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -25582,12 +25692,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -25599,7 +25709,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -25611,12 +25721,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -25628,7 +25738,7 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -25685,15 +25795,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -25704,10 +25814,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -25718,10 +25828,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -25735,7 +25845,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C5" s="30"/>
       <c r="D5" s="30"/>
@@ -25749,7 +25859,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -25763,7 +25873,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
@@ -25774,18 +25884,18 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>48</v>
@@ -25796,7 +25906,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>100</v>
@@ -25807,7 +25917,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>59</v>
@@ -25818,7 +25928,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>73</v>
@@ -25829,7 +25939,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B14" s="16" t="n">
         <v>87</v>
@@ -25840,7 +25950,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>110</v>
@@ -25851,7 +25961,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>86</v>
@@ -25862,7 +25972,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B17" s="16" t="n">
         <v>83</v>
@@ -25873,7 +25983,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>213</v>
@@ -25884,7 +25994,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>434</v>
@@ -25895,7 +26005,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B20" s="16" t="n">
         <v>590</v>
@@ -25906,7 +26016,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B21" s="16" t="n">
         <v>735</v>
@@ -25917,7 +26027,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B22" s="25" t="n">
         <f aca="false">SUM(B10:B21)</f>
@@ -25930,7 +26040,7 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C23" s="31" t="n">
         <f aca="false">C22/B22</f>
@@ -25939,20 +26049,20 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B27" s="16" t="n">
         <v>1949</v>
@@ -25960,7 +26070,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B28" s="16" t="n">
         <v>112</v>
@@ -25968,7 +26078,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B29" s="16" t="n">
         <v>10</v>
@@ -25976,7 +26086,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B30" s="16" t="n">
         <v>2</v>
@@ -25984,7 +26094,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B31" s="19" t="n">
         <f aca="false">SUM(B27:B30)</f>
@@ -25993,7 +26103,7 @@
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -26005,7 +26115,7 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -26017,7 +26127,7 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -26029,12 +26139,12 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
@@ -26046,7 +26156,7 @@
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="23" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
@@ -26058,12 +26168,12 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
@@ -26075,7 +26185,7 @@
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
@@ -26087,12 +26197,12 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
@@ -26104,7 +26214,7 @@
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -26165,15 +26275,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -26184,10 +26294,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -26198,10 +26308,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -26215,7 +26325,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -26226,7 +26336,7 @@
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -26238,7 +26348,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -26250,7 +26360,7 @@
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -26262,12 +26372,12 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -26279,12 +26389,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -26296,12 +26406,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B18" s="23"/>
       <c r="C18" s="23"/>
@@ -26354,15 +26464,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -26373,10 +26483,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -26387,10 +26497,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -26404,7 +26514,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -26418,7 +26528,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -26429,7 +26539,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -26441,7 +26551,7 @@
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -26453,7 +26563,7 @@
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -26465,12 +26575,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -26482,12 +26592,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -26499,7 +26609,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -26511,12 +26621,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -26528,7 +26638,7 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -26573,7 +26683,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -26585,15 +26695,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -26604,10 +26714,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -26618,10 +26728,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -26635,7 +26745,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -26646,15 +26756,15 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B8" s="32" t="n">
         <v>56.8</v>
@@ -26662,7 +26772,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B9" s="32" t="n">
         <v>24.2</v>
@@ -26670,7 +26780,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B10" s="31" t="n">
         <f aca="false">SUM(B8:B9)</f>
@@ -26679,12 +26789,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
@@ -26696,12 +26806,12 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -26713,7 +26823,7 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -26725,12 +26835,12 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
@@ -26740,8 +26850,20 @@
       <c r="G30" s="21"/>
       <c r="H30" s="21"/>
     </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="23" t="s">
+        <v>515</v>
+      </c>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
@@ -26750,6 +26872,7 @@
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A31:H31"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" location="page=167" display="영도구 제1차 탄소중립·녹색성장 기본계획(2025), 부록 설문보고서"/>
@@ -26782,15 +26905,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -26801,10 +26924,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -26815,10 +26938,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -26832,7 +26955,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -26843,7 +26966,7 @@
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -26855,7 +26978,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -26867,7 +26990,7 @@
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -26879,7 +27002,7 @@
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -26891,12 +27014,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -26908,12 +27031,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -26925,12 +27048,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -26942,7 +27065,7 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -26997,15 +27120,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -27016,10 +27139,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -27030,10 +27153,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -27047,7 +27170,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -27061,7 +27184,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -27075,7 +27198,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
@@ -27089,7 +27212,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -27100,60 +27223,60 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -27165,7 +27288,7 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -27177,12 +27300,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
@@ -27194,7 +27317,7 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
@@ -27206,12 +27329,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -27223,7 +27346,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -27281,15 +27404,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -27300,10 +27423,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -27314,10 +27437,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -27331,7 +27454,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -27342,27 +27465,27 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>564</v>
@@ -27384,7 +27507,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>7658</v>
@@ -27406,7 +27529,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>27568</v>
@@ -27428,12 +27551,12 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -27445,12 +27568,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -27462,7 +27585,7 @@
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -27474,12 +27597,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -27491,7 +27614,7 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
@@ -27672,25 +27795,25 @@
         <v>75</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27701,28 +27824,28 @@
         <v>58</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>69</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27730,31 +27853,31 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>60</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27762,10 +27885,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>68</v>
@@ -27774,19 +27897,19 @@
         <v>69</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27794,10 +27917,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>68</v>
@@ -27806,19 +27929,19 @@
         <v>69</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27826,31 +27949,31 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>69</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27858,31 +27981,31 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>69</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27890,31 +28013,31 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>69</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27922,31 +28045,31 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>69</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27954,31 +28077,31 @@
         <v>12</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>69</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>26</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27986,31 +28109,31 @@
         <v>13</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>69</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28018,31 +28141,31 @@
         <v>14</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>69</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28050,31 +28173,31 @@
         <v>15</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -28105,293 +28228,293 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="33" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
   </sheetData>
@@ -28449,15 +28572,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -28468,10 +28591,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -28482,10 +28605,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -28499,7 +28622,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -28510,21 +28633,21 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>552</v>
@@ -28532,10 +28655,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>366024</v>
@@ -28543,10 +28666,10 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>241529</v>
@@ -28554,10 +28677,10 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>171</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>169</v>
       </c>
       <c r="C11" s="16" t="n">
         <v>124495</v>
@@ -28565,10 +28688,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C12" s="16" t="n">
         <v>63</v>
@@ -28576,10 +28699,10 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C13" s="16" t="n">
         <v>5</v>
@@ -28587,10 +28710,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C14" s="16" t="n">
         <v>58</v>
@@ -28598,10 +28721,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C15" s="16" t="n">
         <v>127</v>
@@ -28609,10 +28732,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C16" s="16" t="n">
         <v>32</v>
@@ -28620,10 +28743,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>95</v>
@@ -28631,10 +28754,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C18" s="16" t="n">
         <v>3661</v>
@@ -28642,10 +28765,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>85</v>
@@ -28653,10 +28776,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C20" s="16" t="n">
         <v>146</v>
@@ -28664,10 +28787,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C21" s="16" t="n">
         <v>28</v>
@@ -28675,10 +28798,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C22" s="16" t="n">
         <v>378</v>
@@ -28686,19 +28809,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>186</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>184</v>
       </c>
       <c r="C24" s="16" t="n">
         <v>3</v>
@@ -28706,19 +28829,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C26" s="16" t="n">
         <v>124</v>
@@ -28726,10 +28849,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="16" t="n">
         <v>105</v>
@@ -28737,10 +28860,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C28" s="16" t="n">
         <v>290</v>
@@ -28748,10 +28871,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C29" s="16" t="n">
         <v>363</v>
@@ -28759,10 +28882,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C30" s="16" t="n">
         <v>316852</v>
@@ -28770,10 +28893,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C31" s="16" t="n">
         <v>312779</v>
@@ -28781,10 +28904,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C32" s="16" t="n">
         <v>4073</v>
@@ -28792,23 +28915,23 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B36" s="16" t="n">
         <v>366024</v>
@@ -28820,7 +28943,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B37" s="16" t="n">
         <v>316852</v>
@@ -28832,7 +28955,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B38" s="16" t="n">
         <v>127</v>
@@ -28844,7 +28967,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B39" s="16" t="n">
         <v>63</v>
@@ -28856,7 +28979,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B40" s="19" t="n">
         <f aca="false">SUM(B36:B39)</f>
@@ -28869,12 +28992,12 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
@@ -28886,7 +29009,7 @@
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
@@ -28898,7 +29021,7 @@
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
@@ -28910,12 +29033,12 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
@@ -28927,7 +29050,7 @@
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
@@ -28939,7 +29062,7 @@
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
@@ -28951,12 +29074,12 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="21" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
@@ -28968,7 +29091,7 @@
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
@@ -29024,15 +29147,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -29043,10 +29166,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -29057,10 +29180,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -29074,7 +29197,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -29088,7 +29211,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -29102,7 +29225,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
@@ -29113,21 +29236,21 @@
     </row>
     <row r="9" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>988</v>
@@ -29142,7 +29265,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>4769</v>
@@ -29157,7 +29280,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>11936</v>
@@ -29172,12 +29295,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -29185,7 +29308,7 @@
     </row>
     <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -29193,12 +29316,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
@@ -29210,7 +29333,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
@@ -29222,12 +29345,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
@@ -29239,7 +29362,7 @@
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -29251,12 +29374,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
@@ -29268,7 +29391,7 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
@@ -29327,15 +29450,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -29346,10 +29469,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -29360,10 +29483,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -29377,7 +29500,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -29391,7 +29514,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -29402,7 +29525,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B8" s="24" t="n">
         <v>834</v>
@@ -29410,7 +29533,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B9" s="24" t="n">
         <v>8760</v>
@@ -29418,27 +29541,27 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>79164</v>
@@ -29458,7 +29581,7 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>81885</v>
@@ -29478,7 +29601,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B14" s="16" t="n">
         <v>92253</v>
@@ -29498,7 +29621,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>110334</v>
@@ -29518,7 +29641,7 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>101161</v>
@@ -29538,7 +29661,7 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B17" s="16" t="n">
         <v>108400</v>
@@ -29558,7 +29681,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>101292</v>
@@ -29578,7 +29701,7 @@
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>82236</v>
@@ -29598,7 +29721,7 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B20" s="16" t="n">
         <v>65990</v>
@@ -29618,7 +29741,7 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B21" s="16" t="n">
         <v>83948</v>
@@ -29638,7 +29761,7 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B22" s="16" t="n">
         <v>77766</v>
@@ -29658,7 +29781,7 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B23" s="16" t="n">
         <v>79478</v>
@@ -29678,7 +29801,7 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">SUM(B12:B23)</f>
@@ -29703,7 +29826,7 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B25" s="25" t="n">
         <f aca="false">B24/$B$8</f>
@@ -29728,7 +29851,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B26" s="26" t="n">
         <f aca="false">B24/($B$8*$B$9)</f>
@@ -29753,23 +29876,23 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B31" s="27" t="n">
         <v>0</v>
@@ -29780,7 +29903,7 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B32" s="27" t="n">
         <v>0</v>
@@ -29791,7 +29914,7 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B33" s="27" t="n">
         <v>0</v>
@@ -29802,7 +29925,7 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B34" s="27" t="n">
         <v>0</v>
@@ -29813,7 +29936,7 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B35" s="27" t="n">
         <v>0</v>
@@ -29824,7 +29947,7 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B36" s="27" t="n">
         <v>0</v>
@@ -29835,7 +29958,7 @@
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B37" s="27" t="n">
         <v>0</v>
@@ -29846,7 +29969,7 @@
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B38" s="27" t="n">
         <v>0.2</v>
@@ -29857,7 +29980,7 @@
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B39" s="27" t="n">
         <v>57</v>
@@ -29868,7 +29991,7 @@
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B40" s="27" t="n">
         <v>222</v>
@@ -29879,7 +30002,7 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B41" s="27" t="n">
         <v>374.8</v>
@@ -29890,7 +30013,7 @@
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B42" s="27" t="n">
         <v>464.1</v>
@@ -29901,7 +30024,7 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B43" s="27" t="n">
         <v>477.8</v>
@@ -29912,7 +30035,7 @@
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B44" s="27" t="n">
         <v>441.5</v>
@@ -29923,7 +30046,7 @@
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B45" s="27" t="n">
         <v>377.1</v>
@@ -29934,7 +30057,7 @@
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B46" s="27" t="n">
         <v>202.5</v>
@@ -29945,7 +30068,7 @@
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B47" s="27" t="n">
         <v>57.9</v>
@@ -29956,7 +30079,7 @@
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B48" s="27" t="n">
         <v>3.4</v>
@@ -29967,7 +30090,7 @@
     </row>
     <row r="49" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B49" s="27" t="n">
         <v>0</v>
@@ -29978,7 +30101,7 @@
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B50" s="27" t="n">
         <v>0</v>
@@ -29989,7 +30112,7 @@
     </row>
     <row r="51" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B51" s="27" t="n">
         <v>0</v>
@@ -30000,7 +30123,7 @@
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B52" s="27" t="n">
         <v>0</v>
@@ -30011,7 +30134,7 @@
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B53" s="27" t="n">
         <v>0</v>
@@ -30022,7 +30145,7 @@
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B54" s="27" t="n">
         <v>0</v>
@@ -30033,17 +30156,17 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
@@ -30055,7 +30178,7 @@
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="21" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
@@ -30067,7 +30190,7 @@
     </row>
     <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="21" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -30079,12 +30202,12 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="21" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
@@ -30096,7 +30219,7 @@
     </row>
     <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="21" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
@@ -30108,12 +30231,12 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="21" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
@@ -30125,7 +30248,7 @@
     </row>
     <row r="68" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B68" s="23"/>
       <c r="C68" s="23"/>
@@ -30137,7 +30260,7 @@
     </row>
     <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B69" s="23"/>
       <c r="C69" s="23"/>
@@ -30195,15 +30318,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -30214,10 +30337,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -30228,10 +30351,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -30245,7 +30368,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -30259,7 +30382,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -30270,7 +30393,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -30282,7 +30405,7 @@
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -30294,7 +30417,7 @@
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -30306,7 +30429,7 @@
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -30318,12 +30441,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -30335,7 +30458,7 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -30347,12 +30470,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
@@ -30364,7 +30487,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -30376,12 +30499,12 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
@@ -30393,7 +30516,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
@@ -30451,15 +30574,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -30470,10 +30593,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -30484,10 +30607,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -30501,7 +30624,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -30512,21 +30635,21 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>1361391267</v>
@@ -30541,7 +30664,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>1330081880</v>
@@ -30556,7 +30679,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>1275954471</v>
@@ -30571,7 +30694,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>1255492164</v>
@@ -30586,7 +30709,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>1196183526</v>
@@ -30601,7 +30724,7 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>1267916346</v>
@@ -30616,7 +30739,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B14" s="16" t="n">
         <v>1485107130</v>
@@ -30631,7 +30754,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>1594535800</v>
@@ -30646,7 +30769,7 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>1596714320</v>
@@ -30661,7 +30784,7 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B17" s="16" t="n">
         <v>1274725178</v>
@@ -30676,7 +30799,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>1231658485</v>
@@ -30691,7 +30814,7 @@
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>1312891989</v>
@@ -30706,7 +30829,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B20" s="25" t="n">
         <f aca="false">SUM(B8:B19)</f>
@@ -30723,7 +30846,7 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B21" s="19" t="n">
         <f aca="false">B20/1000000</f>
@@ -30740,7 +30863,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B22" s="20" t="n">
         <f aca="false">B20/D20</f>
@@ -30749,7 +30872,7 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B23" s="29" t="n">
         <v>48396</v>
@@ -30760,12 +30883,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
@@ -30777,7 +30900,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -30789,12 +30912,12 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
@@ -30806,7 +30929,7 @@
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -30818,12 +30941,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
@@ -30835,7 +30958,7 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
@@ -30888,15 +31011,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -30907,10 +31030,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -30921,10 +31044,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -30938,7 +31061,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -30952,7 +31075,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -30963,18 +31086,18 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>1017947</v>
@@ -30985,7 +31108,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>893751</v>
@@ -30996,7 +31119,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>925138</v>
@@ -31007,7 +31130,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>865606</v>
@@ -31018,7 +31141,7 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>929584</v>
@@ -31029,7 +31152,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B14" s="16" t="n">
         <v>1115212</v>
@@ -31040,7 +31163,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>1361460</v>
@@ -31051,7 +31174,7 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>1445503</v>
@@ -31062,7 +31185,7 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B17" s="16" t="n">
         <v>1259064</v>
@@ -31073,7 +31196,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>1007744</v>
@@ -31084,7 +31207,7 @@
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>889789</v>
@@ -31095,7 +31218,7 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B20" s="16" t="n">
         <v>987412</v>
@@ -31106,7 +31229,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B21" s="25" t="n">
         <f aca="false">SUM(B9:B20)</f>
@@ -31119,7 +31242,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B22" s="19" t="n">
         <f aca="false">AVERAGE(B9:B20)</f>
@@ -31132,26 +31255,26 @@
     </row>
     <row r="24" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
@@ -31163,7 +31286,7 @@
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
@@ -31175,12 +31298,12 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -31192,7 +31315,7 @@
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
@@ -31204,12 +31327,12 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
@@ -31221,7 +31344,7 @@
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
@@ -31279,15 +31402,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -31298,10 +31421,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -31312,10 +31435,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -31329,7 +31452,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -31340,21 +31463,21 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>240</v>
@@ -31362,10 +31485,10 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>395</v>
@@ -31373,10 +31496,10 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>220</v>
@@ -31384,10 +31507,10 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C11" s="16" t="n">
         <v>355</v>
@@ -31395,10 +31518,10 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C12" s="16" t="n">
         <v>25</v>
@@ -31406,10 +31529,10 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C13" s="16" t="n">
         <v>0</v>
@@ -31417,10 +31540,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C14" s="16" t="n">
         <v>153</v>
@@ -31428,10 +31551,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C15" s="16" t="n">
         <v>1391</v>
@@ -31439,10 +31562,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C16" s="16" t="n">
         <v>1571</v>
@@ -31450,10 +31573,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>361</v>
@@ -31461,23 +31584,23 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B21" s="28" t="n">
         <f aca="false">SUMIF($A$8:$A$17,"LED등",$C$8:$C$17)</f>
@@ -31490,7 +31613,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B22" s="28" t="n">
         <f aca="false">SUMIF($A$8:$A$17,"나트륨등",$C$8:$C$17)</f>
@@ -31503,7 +31626,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B23" s="28" t="n">
         <f aca="false">SUMIF($A$8:$A$17,"일반메탈등",$C$8:$C$17)</f>
@@ -31516,7 +31639,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B24" s="19" t="n">
         <f aca="false">SUM(B21:B23)</f>
@@ -31525,12 +31648,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -31542,7 +31665,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -31554,12 +31677,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -31571,7 +31694,7 @@
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -31583,12 +31706,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -31600,7 +31723,7 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>

--- a/data/busan-energy-teacher-data.xlsx
+++ b/data/busan-energy-teacher-data.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="649">
   <si>
     <r>
       <rPr>
@@ -2697,7 +2697,31 @@
     <t xml:space="preserve">고효율기기 및 스마트에너지 보급</t>
   </si>
   <si>
-    <t xml:space="preserve">고효율 조명 교체</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고효율 조명 교체 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공공건물 냉방기 고효율 교체</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2790,7 +2814,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(kWh)</t>
+      <t xml:space="preserve">(kWh), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">폭염 정도에 따른 냉방 절감량</t>
     </r>
   </si>
   <si>
@@ -3180,6 +3212,33 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">혁신기업 기술개발 지원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사업화 지원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">□ 어떤 기준으로 지원 기업을 고르는가</t>
     </r>
     <r>
@@ -3238,6 +3297,57 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">지원 기업 수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성과 비율을 가정한 예상 성과 기업 수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차시 계산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">인증</t>
     </r>
     <r>
@@ -3255,7 +3365,17 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">시제품</t>
+      <t xml:space="preserve">시제품 수</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지원 기업의 매출</t>
     </r>
     <r>
       <rPr>
@@ -3272,33 +3392,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">특허 수</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지원 기업의 매출</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">일자리</t>
     </r>
     <r>
@@ -3335,15 +3428,32 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지원 후 무엇이 달라졌는지 자료가 필요합니다</t>
+      <t xml:space="preserve">. 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차시의 지원 기업 수는 산출이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지원 후 무엇이 달라졌는지는 이후 자료로 확인해야 합니다</t>
     </r>
     <r>
       <rPr>
@@ -4338,7 +4448,48 @@
     <t xml:space="preserve">시민참여형 발전사업 활성화</t>
   </si>
   <si>
-    <t xml:space="preserve">시민참여 미니태양광 지원</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시민참여 미니태양광 지원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시민 에너지 교육</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설명회</t>
+    </r>
   </si>
   <si>
     <r>
@@ -19391,11 +19542,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="39251896"/>
-        <c:axId val="29905600"/>
+        <c:axId val="20060684"/>
+        <c:axId val="76178250"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="39251896"/>
+        <c:axId val="20060684"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19427,7 +19578,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29905600"/>
+        <c:crossAx val="76178250"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -19435,7 +19586,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29905600"/>
+        <c:axId val="76178250"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19511,7 +19662,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39251896"/>
+        <c:crossAx val="20060684"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19748,11 +19899,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="92791558"/>
-        <c:axId val="80891113"/>
+        <c:axId val="37404632"/>
+        <c:axId val="62491949"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="92791558"/>
+        <c:axId val="37404632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19784,7 +19935,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80891113"/>
+        <c:crossAx val="62491949"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -19792,7 +19943,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80891113"/>
+        <c:axId val="62491949"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19868,7 +20019,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92791558"/>
+        <c:crossAx val="37404632"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20045,11 +20196,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="65943338"/>
-        <c:axId val="3436774"/>
+        <c:axId val="94803817"/>
+        <c:axId val="11802798"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="65943338"/>
+        <c:axId val="94803817"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20081,7 +20232,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3436774"/>
+        <c:crossAx val="11802798"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -20089,7 +20240,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="3436774"/>
+        <c:axId val="11802798"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20165,7 +20316,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65943338"/>
+        <c:crossAx val="94803817"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20516,11 +20667,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="27319620"/>
-        <c:axId val="30894230"/>
+        <c:axId val="92233088"/>
+        <c:axId val="77664110"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="27319620"/>
+        <c:axId val="92233088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20552,7 +20703,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30894230"/>
+        <c:crossAx val="77664110"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -20560,7 +20711,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30894230"/>
+        <c:axId val="77664110"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20636,7 +20787,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27319620"/>
+        <c:crossAx val="92233088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20819,11 +20970,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="1691639"/>
-        <c:axId val="90164455"/>
+        <c:axId val="27735691"/>
+        <c:axId val="21774375"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1691639"/>
+        <c:axId val="27735691"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20855,7 +21006,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90164455"/>
+        <c:crossAx val="21774375"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -20863,7 +21014,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90164455"/>
+        <c:axId val="21774375"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20939,7 +21090,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1691639"/>
+        <c:crossAx val="27735691"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -21475,11 +21626,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="41254945"/>
-        <c:axId val="76221491"/>
+        <c:axId val="13739015"/>
+        <c:axId val="54242966"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="41254945"/>
+        <c:axId val="13739015"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -21511,7 +21662,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76221491"/>
+        <c:crossAx val="54242966"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -21519,7 +21670,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76221491"/>
+        <c:axId val="54242966"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -21595,7 +21746,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41254945"/>
+        <c:crossAx val="13739015"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -22131,11 +22282,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="48627952"/>
-        <c:axId val="68870586"/>
+        <c:axId val="8788507"/>
+        <c:axId val="25153080"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="48627952"/>
+        <c:axId val="8788507"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22167,7 +22318,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68870586"/>
+        <c:crossAx val="25153080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -22175,7 +22326,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="68870586"/>
+        <c:axId val="25153080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22251,7 +22402,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48627952"/>
+        <c:crossAx val="8788507"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -22626,11 +22777,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="11537016"/>
-        <c:axId val="74691838"/>
+        <c:axId val="483919"/>
+        <c:axId val="40394143"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="11537016"/>
+        <c:axId val="483919"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22662,7 +22813,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74691838"/>
+        <c:crossAx val="40394143"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -22670,7 +22821,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74691838"/>
+        <c:axId val="40394143"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22746,7 +22897,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11537016"/>
+        <c:crossAx val="483919"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -22983,11 +23134,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="5091141"/>
-        <c:axId val="37562803"/>
+        <c:axId val="69847881"/>
+        <c:axId val="73692831"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5091141"/>
+        <c:axId val="69847881"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -23019,7 +23170,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37562803"/>
+        <c:crossAx val="73692831"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -23027,7 +23178,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37562803"/>
+        <c:axId val="73692831"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -23103,7 +23254,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5091141"/>
+        <c:crossAx val="69847881"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -23340,11 +23491,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="6919180"/>
-        <c:axId val="11152629"/>
+        <c:axId val="56585128"/>
+        <c:axId val="33638636"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="6919180"/>
+        <c:axId val="56585128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -23376,7 +23527,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11152629"/>
+        <c:crossAx val="33638636"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -23384,7 +23535,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11152629"/>
+        <c:axId val="33638636"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -23460,7 +23611,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6919180"/>
+        <c:crossAx val="56585128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -23643,11 +23794,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="64184646"/>
-        <c:axId val="89479679"/>
+        <c:axId val="52658465"/>
+        <c:axId val="88314401"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="64184646"/>
+        <c:axId val="52658465"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -23679,7 +23830,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89479679"/>
+        <c:crossAx val="88314401"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -23687,7 +23838,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89479679"/>
+        <c:axId val="88314401"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -23763,7 +23914,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64184646"/>
+        <c:crossAx val="52658465"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -23946,11 +24097,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="12928499"/>
-        <c:axId val="83618270"/>
+        <c:axId val="27326811"/>
+        <c:axId val="65095608"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="12928499"/>
+        <c:axId val="27326811"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -23982,7 +24133,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83618270"/>
+        <c:crossAx val="65095608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -23990,7 +24141,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83618270"/>
+        <c:axId val="65095608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -24066,7 +24217,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12928499"/>
+        <c:crossAx val="27326811"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -24974,15 +25125,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -24993,10 +25144,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -25007,10 +25158,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -25024,7 +25175,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -25038,7 +25189,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -25052,7 +25203,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
@@ -25066,7 +25217,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -25077,68 +25228,68 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -25150,7 +25301,7 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -25162,12 +25313,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
@@ -25179,7 +25330,7 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -25191,12 +25342,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -25208,7 +25359,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -25267,15 +25418,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -25286,10 +25437,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -25300,10 +25451,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -25317,7 +25468,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -25331,7 +25482,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -25342,15 +25493,15 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>50</v>
@@ -25358,7 +25509,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>130</v>
@@ -25366,7 +25517,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>300</v>
@@ -25377,68 +25528,68 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
@@ -25450,7 +25601,7 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -25462,12 +25613,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -25479,7 +25630,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -25491,12 +25642,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -25508,7 +25659,7 @@
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -25564,15 +25715,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -25583,10 +25734,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -25597,10 +25748,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -25614,7 +25765,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -25628,7 +25779,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -25639,7 +25790,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -25651,7 +25802,7 @@
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -25663,7 +25814,7 @@
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -25675,12 +25826,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -25692,12 +25843,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -25709,7 +25860,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -25721,12 +25872,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -25738,7 +25889,7 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -25795,15 +25946,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -25814,10 +25965,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -25828,10 +25979,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -25845,7 +25996,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C5" s="30"/>
       <c r="D5" s="30"/>
@@ -25859,7 +26010,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -25873,7 +26024,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
@@ -25884,18 +26035,18 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>48</v>
@@ -25906,7 +26057,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>100</v>
@@ -25917,7 +26068,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>59</v>
@@ -25928,7 +26079,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>73</v>
@@ -25939,7 +26090,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B14" s="16" t="n">
         <v>87</v>
@@ -25950,7 +26101,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>110</v>
@@ -25961,7 +26112,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>86</v>
@@ -25972,7 +26123,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B17" s="16" t="n">
         <v>83</v>
@@ -25983,7 +26134,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>213</v>
@@ -25994,7 +26145,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>434</v>
@@ -26005,7 +26156,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B20" s="16" t="n">
         <v>590</v>
@@ -26016,7 +26167,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B21" s="16" t="n">
         <v>735</v>
@@ -26027,7 +26178,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B22" s="25" t="n">
         <f aca="false">SUM(B10:B21)</f>
@@ -26040,7 +26191,7 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C23" s="31" t="n">
         <f aca="false">C22/B22</f>
@@ -26049,20 +26200,20 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B27" s="16" t="n">
         <v>1949</v>
@@ -26070,7 +26221,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B28" s="16" t="n">
         <v>112</v>
@@ -26078,7 +26229,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B29" s="16" t="n">
         <v>10</v>
@@ -26086,7 +26237,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B30" s="16" t="n">
         <v>2</v>
@@ -26094,7 +26245,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B31" s="19" t="n">
         <f aca="false">SUM(B27:B30)</f>
@@ -26103,7 +26254,7 @@
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -26115,7 +26266,7 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -26127,7 +26278,7 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -26139,12 +26290,12 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
@@ -26156,7 +26307,7 @@
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
@@ -26168,12 +26319,12 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
@@ -26185,7 +26336,7 @@
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
@@ -26197,12 +26348,12 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
@@ -26214,7 +26365,7 @@
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -26275,15 +26426,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -26294,10 +26445,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -26308,10 +26459,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -26325,7 +26476,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -26336,7 +26487,7 @@
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -26348,7 +26499,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -26360,7 +26511,7 @@
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -26372,12 +26523,12 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -26389,12 +26540,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -26406,12 +26557,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B18" s="23"/>
       <c r="C18" s="23"/>
@@ -26464,15 +26615,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -26483,10 +26634,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -26497,10 +26648,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -26514,7 +26665,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -26528,7 +26679,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -26539,7 +26690,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -26551,7 +26702,7 @@
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -26563,7 +26714,7 @@
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -26575,12 +26726,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -26592,12 +26743,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -26609,7 +26760,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -26621,12 +26772,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -26638,7 +26789,7 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -26695,15 +26846,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -26714,10 +26865,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -26728,10 +26879,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -26745,7 +26896,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -26756,15 +26907,15 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B8" s="32" t="n">
         <v>56.8</v>
@@ -26772,7 +26923,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B9" s="32" t="n">
         <v>24.2</v>
@@ -26780,7 +26931,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B10" s="31" t="n">
         <f aca="false">SUM(B8:B9)</f>
@@ -26789,12 +26940,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
@@ -26806,12 +26957,12 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -26823,7 +26974,7 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -26835,12 +26986,12 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
@@ -26852,7 +27003,7 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
@@ -26905,15 +27056,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -26924,10 +27075,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -26938,10 +27089,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -26955,7 +27106,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -26966,7 +27117,7 @@
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -26978,7 +27129,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -26990,7 +27141,7 @@
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -27002,7 +27153,7 @@
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -27014,12 +27165,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -27031,12 +27182,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -27048,12 +27199,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -27065,7 +27216,7 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -27120,15 +27271,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -27139,10 +27290,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -27153,10 +27304,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -27170,7 +27321,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -27184,7 +27335,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -27198,7 +27349,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
@@ -27212,7 +27363,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -27223,60 +27374,60 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -27288,7 +27439,7 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -27300,12 +27451,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
@@ -27317,7 +27468,7 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
@@ -27329,12 +27480,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -27346,7 +27497,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -27404,15 +27555,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -27423,10 +27574,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -27437,10 +27588,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -27454,7 +27605,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -27465,27 +27616,27 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>564</v>
@@ -27507,7 +27658,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>7658</v>
@@ -27529,7 +27680,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>27568</v>
@@ -27551,12 +27702,12 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -27568,12 +27719,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -27585,7 +27736,7 @@
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -27597,12 +27748,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -27614,7 +27765,7 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
@@ -27955,25 +28106,25 @@
         <v>110</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27984,7 +28135,7 @@
         <v>109</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>83</v>
@@ -27993,19 +28144,19 @@
         <v>69</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28016,7 +28167,7 @@
         <v>109</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>83</v>
@@ -28025,19 +28176,19 @@
         <v>69</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28048,7 +28199,7 @@
         <v>109</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>83</v>
@@ -28057,19 +28208,19 @@
         <v>69</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28080,7 +28231,7 @@
         <v>109</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>83</v>
@@ -28089,19 +28240,19 @@
         <v>69</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>26</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28109,10 +28260,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>83</v>
@@ -28121,19 +28272,19 @@
         <v>69</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28141,10 +28292,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>83</v>
@@ -28153,19 +28304,19 @@
         <v>69</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28173,31 +28324,31 @@
         <v>15</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>60</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -28228,293 +28379,293 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="33" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
   </sheetData>
@@ -28572,15 +28723,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -28591,10 +28742,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -28605,10 +28756,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -28622,7 +28773,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -28633,21 +28784,21 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>552</v>
@@ -28655,10 +28806,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>366024</v>
@@ -28666,10 +28817,10 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>172</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>171</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>241529</v>
@@ -28677,10 +28828,10 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" s="16" t="n">
         <v>124495</v>
@@ -28688,10 +28839,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" s="16" t="n">
         <v>63</v>
@@ -28699,10 +28850,10 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" s="16" t="n">
         <v>5</v>
@@ -28710,10 +28861,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" s="16" t="n">
         <v>58</v>
@@ -28721,10 +28872,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="16" t="n">
         <v>127</v>
@@ -28732,10 +28883,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" s="16" t="n">
         <v>32</v>
@@ -28743,10 +28894,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>95</v>
@@ -28754,10 +28905,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C18" s="16" t="n">
         <v>3661</v>
@@ -28765,10 +28916,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>85</v>
@@ -28776,10 +28927,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C20" s="16" t="n">
         <v>146</v>
@@ -28787,10 +28938,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="B21" s="14" t="s">
         <v>184</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>183</v>
       </c>
       <c r="C21" s="16" t="n">
         <v>28</v>
@@ -28798,10 +28949,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C22" s="16" t="n">
         <v>378</v>
@@ -28809,19 +28960,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>187</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>186</v>
       </c>
       <c r="C23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C24" s="16" t="n">
         <v>3</v>
@@ -28829,19 +28980,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C26" s="16" t="n">
         <v>124</v>
@@ -28849,10 +29000,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="16" t="n">
         <v>105</v>
@@ -28860,10 +29011,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C28" s="16" t="n">
         <v>290</v>
@@ -28871,10 +29022,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C29" s="16" t="n">
         <v>363</v>
@@ -28882,10 +29033,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C30" s="16" t="n">
         <v>316852</v>
@@ -28893,10 +29044,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" s="16" t="n">
         <v>312779</v>
@@ -28904,10 +29055,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C32" s="16" t="n">
         <v>4073</v>
@@ -28915,23 +29066,23 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B36" s="16" t="n">
         <v>366024</v>
@@ -28943,7 +29094,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B37" s="16" t="n">
         <v>316852</v>
@@ -28955,7 +29106,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B38" s="16" t="n">
         <v>127</v>
@@ -28967,7 +29118,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B39" s="16" t="n">
         <v>63</v>
@@ -28979,7 +29130,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B40" s="19" t="n">
         <f aca="false">SUM(B36:B39)</f>
@@ -28992,12 +29143,12 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
@@ -29009,7 +29160,7 @@
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
@@ -29021,7 +29172,7 @@
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
@@ -29033,12 +29184,12 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
@@ -29050,7 +29201,7 @@
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
@@ -29062,7 +29213,7 @@
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
@@ -29074,12 +29225,12 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="21" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
@@ -29091,7 +29242,7 @@
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
@@ -29147,15 +29298,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -29166,10 +29317,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -29180,10 +29331,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -29197,7 +29348,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -29211,7 +29362,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -29225,7 +29376,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
@@ -29236,21 +29387,21 @@
     </row>
     <row r="9" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>988</v>
@@ -29265,7 +29416,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>4769</v>
@@ -29280,7 +29431,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>11936</v>
@@ -29295,12 +29446,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -29308,7 +29459,7 @@
     </row>
     <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -29316,12 +29467,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
@@ -29333,7 +29484,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
@@ -29345,12 +29496,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
@@ -29362,7 +29513,7 @@
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -29374,12 +29525,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
@@ -29391,7 +29542,7 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
@@ -29450,15 +29601,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -29469,10 +29620,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -29483,10 +29634,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -29500,7 +29651,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -29514,7 +29665,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -29525,7 +29676,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B8" s="24" t="n">
         <v>834</v>
@@ -29533,7 +29684,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B9" s="24" t="n">
         <v>8760</v>
@@ -29541,27 +29692,27 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>79164</v>
@@ -29581,7 +29732,7 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>81885</v>
@@ -29601,7 +29752,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B14" s="16" t="n">
         <v>92253</v>
@@ -29621,7 +29772,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>110334</v>
@@ -29641,7 +29792,7 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>101161</v>
@@ -29661,7 +29812,7 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B17" s="16" t="n">
         <v>108400</v>
@@ -29681,7 +29832,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>101292</v>
@@ -29701,7 +29852,7 @@
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>82236</v>
@@ -29721,7 +29872,7 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B20" s="16" t="n">
         <v>65990</v>
@@ -29741,7 +29892,7 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B21" s="16" t="n">
         <v>83948</v>
@@ -29761,7 +29912,7 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B22" s="16" t="n">
         <v>77766</v>
@@ -29781,7 +29932,7 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B23" s="16" t="n">
         <v>79478</v>
@@ -29801,7 +29952,7 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">SUM(B12:B23)</f>
@@ -29826,7 +29977,7 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B25" s="25" t="n">
         <f aca="false">B24/$B$8</f>
@@ -29851,7 +30002,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" s="26" t="n">
         <f aca="false">B24/($B$8*$B$9)</f>
@@ -29876,23 +30027,23 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B31" s="27" t="n">
         <v>0</v>
@@ -29903,7 +30054,7 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B32" s="27" t="n">
         <v>0</v>
@@ -29914,7 +30065,7 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B33" s="27" t="n">
         <v>0</v>
@@ -29925,7 +30076,7 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B34" s="27" t="n">
         <v>0</v>
@@ -29936,7 +30087,7 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B35" s="27" t="n">
         <v>0</v>
@@ -29947,7 +30098,7 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B36" s="27" t="n">
         <v>0</v>
@@ -29958,7 +30109,7 @@
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B37" s="27" t="n">
         <v>0</v>
@@ -29969,7 +30120,7 @@
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B38" s="27" t="n">
         <v>0.2</v>
@@ -29980,7 +30131,7 @@
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B39" s="27" t="n">
         <v>57</v>
@@ -29991,7 +30142,7 @@
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B40" s="27" t="n">
         <v>222</v>
@@ -30002,7 +30153,7 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B41" s="27" t="n">
         <v>374.8</v>
@@ -30013,7 +30164,7 @@
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B42" s="27" t="n">
         <v>464.1</v>
@@ -30024,7 +30175,7 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B43" s="27" t="n">
         <v>477.8</v>
@@ -30035,7 +30186,7 @@
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B44" s="27" t="n">
         <v>441.5</v>
@@ -30046,7 +30197,7 @@
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B45" s="27" t="n">
         <v>377.1</v>
@@ -30057,7 +30208,7 @@
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B46" s="27" t="n">
         <v>202.5</v>
@@ -30068,7 +30219,7 @@
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B47" s="27" t="n">
         <v>57.9</v>
@@ -30079,7 +30230,7 @@
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B48" s="27" t="n">
         <v>3.4</v>
@@ -30090,7 +30241,7 @@
     </row>
     <row r="49" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B49" s="27" t="n">
         <v>0</v>
@@ -30101,7 +30252,7 @@
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B50" s="27" t="n">
         <v>0</v>
@@ -30112,7 +30263,7 @@
     </row>
     <row r="51" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B51" s="27" t="n">
         <v>0</v>
@@ -30123,7 +30274,7 @@
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B52" s="27" t="n">
         <v>0</v>
@@ -30134,7 +30285,7 @@
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B53" s="27" t="n">
         <v>0</v>
@@ -30145,7 +30296,7 @@
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B54" s="27" t="n">
         <v>0</v>
@@ -30156,17 +30307,17 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
@@ -30178,7 +30329,7 @@
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
@@ -30190,7 +30341,7 @@
     </row>
     <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -30202,12 +30353,12 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
@@ -30219,7 +30370,7 @@
     </row>
     <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="21" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
@@ -30231,12 +30382,12 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="21" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
@@ -30248,7 +30399,7 @@
     </row>
     <row r="68" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="23" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B68" s="23"/>
       <c r="C68" s="23"/>
@@ -30260,7 +30411,7 @@
     </row>
     <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="23" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B69" s="23"/>
       <c r="C69" s="23"/>
@@ -30318,15 +30469,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -30337,10 +30488,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -30351,10 +30502,10 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -30368,7 +30519,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -30382,7 +30533,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -30393,7 +30544,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -30405,7 +30556,7 @@
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -30417,7 +30568,7 @@
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -30429,7 +30580,7 @@
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -30441,12 +30592,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -30458,7 +30609,7 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -30470,12 +30621,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
@@ -30487,7 +30638,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -30499,12 +30650,12 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
@@ -30516,7 +30667,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
@@ -30574,15 +30725,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -30593,10 +30744,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -30607,10 +30758,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -30624,7 +30775,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -30635,21 +30786,21 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>1361391267</v>
@@ -30664,7 +30815,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>1330081880</v>
@@ -30679,7 +30830,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>1275954471</v>
@@ -30694,7 +30845,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>1255492164</v>
@@ -30709,7 +30860,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>1196183526</v>
@@ -30724,7 +30875,7 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>1267916346</v>
@@ -30739,7 +30890,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B14" s="16" t="n">
         <v>1485107130</v>
@@ -30754,7 +30905,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>1594535800</v>
@@ -30769,7 +30920,7 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>1596714320</v>
@@ -30784,7 +30935,7 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B17" s="16" t="n">
         <v>1274725178</v>
@@ -30799,7 +30950,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>1231658485</v>
@@ -30814,7 +30965,7 @@
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>1312891989</v>
@@ -30829,7 +30980,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B20" s="25" t="n">
         <f aca="false">SUM(B8:B19)</f>
@@ -30846,7 +30997,7 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B21" s="19" t="n">
         <f aca="false">B20/1000000</f>
@@ -30863,7 +31014,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B22" s="20" t="n">
         <f aca="false">B20/D20</f>
@@ -30872,7 +31023,7 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B23" s="29" t="n">
         <v>48396</v>
@@ -30883,12 +31034,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
@@ -30900,7 +31051,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -30912,12 +31063,12 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
@@ -30929,7 +31080,7 @@
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -30941,12 +31092,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
@@ -30958,7 +31109,7 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
@@ -31011,15 +31162,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -31030,10 +31181,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -31044,10 +31195,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -31061,7 +31212,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -31075,7 +31226,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -31086,18 +31237,18 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>1017947</v>
@@ -31108,7 +31259,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>893751</v>
@@ -31119,7 +31270,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>925138</v>
@@ -31130,7 +31281,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>865606</v>
@@ -31141,7 +31292,7 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>929584</v>
@@ -31152,7 +31303,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B14" s="16" t="n">
         <v>1115212</v>
@@ -31163,7 +31314,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>1361460</v>
@@ -31174,7 +31325,7 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>1445503</v>
@@ -31185,7 +31336,7 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B17" s="16" t="n">
         <v>1259064</v>
@@ -31196,7 +31347,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>1007744</v>
@@ -31207,7 +31358,7 @@
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>889789</v>
@@ -31218,7 +31369,7 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B20" s="16" t="n">
         <v>987412</v>
@@ -31229,7 +31380,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B21" s="25" t="n">
         <f aca="false">SUM(B9:B20)</f>
@@ -31242,7 +31393,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B22" s="19" t="n">
         <f aca="false">AVERAGE(B9:B20)</f>
@@ -31255,26 +31406,26 @@
     </row>
     <row r="24" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
@@ -31286,7 +31437,7 @@
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
@@ -31298,12 +31449,12 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -31315,7 +31466,7 @@
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
@@ -31327,12 +31478,12 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
@@ -31344,7 +31495,7 @@
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
@@ -31402,15 +31553,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -31421,10 +31572,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -31435,10 +31586,10 @@
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -31452,7 +31603,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -31463,21 +31614,21 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>240</v>
@@ -31485,10 +31636,10 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>395</v>
@@ -31496,10 +31647,10 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>220</v>
@@ -31507,10 +31658,10 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>362</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>361</v>
       </c>
       <c r="C11" s="16" t="n">
         <v>355</v>
@@ -31518,10 +31669,10 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C12" s="16" t="n">
         <v>25</v>
@@ -31529,10 +31680,10 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C13" s="16" t="n">
         <v>0</v>
@@ -31540,10 +31691,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C14" s="16" t="n">
         <v>153</v>
@@ -31551,10 +31702,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C15" s="16" t="n">
         <v>1391</v>
@@ -31562,10 +31713,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C16" s="16" t="n">
         <v>1571</v>
@@ -31573,10 +31724,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>361</v>
@@ -31584,23 +31735,23 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B21" s="28" t="n">
         <f aca="false">SUMIF($A$8:$A$17,"LED등",$C$8:$C$17)</f>
@@ -31613,7 +31764,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B22" s="28" t="n">
         <f aca="false">SUMIF($A$8:$A$17,"나트륨등",$C$8:$C$17)</f>
@@ -31626,7 +31777,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B23" s="28" t="n">
         <f aca="false">SUMIF($A$8:$A$17,"일반메탈등",$C$8:$C$17)</f>
@@ -31639,7 +31790,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B24" s="19" t="n">
         <f aca="false">SUM(B21:B23)</f>
@@ -31648,12 +31799,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -31665,7 +31816,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -31677,12 +31828,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -31694,7 +31845,7 @@
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -31706,12 +31857,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -31723,7 +31874,7 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
